--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/150.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/150.xlsx
@@ -426,13 +426,13 @@
         <v>-13.10962361583298</v>
       </c>
       <c r="E2">
-        <v>-20.50434821029199</v>
+        <v>-17.89351086285774</v>
       </c>
       <c r="F2">
-        <v>-5.48905497189022</v>
+        <v>-4.9000940321738</v>
       </c>
       <c r="G2">
-        <v>-17.79638815576048</v>
+        <v>-14.90964981768922</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-12.88883715829503</v>
       </c>
       <c r="E3">
-        <v>-20.56484862303447</v>
+        <v>-18.98822416947197</v>
       </c>
       <c r="F3">
-        <v>-5.867775436408723</v>
+        <v>-4.959837545998505</v>
       </c>
       <c r="G3">
-        <v>-18.24832720725059</v>
+        <v>-15.1048808598654</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-12.63858720095531</v>
       </c>
       <c r="E4">
-        <v>-21.31009053352876</v>
+        <v>-18.52839839025911</v>
       </c>
       <c r="F4">
-        <v>-5.534480983524939</v>
+        <v>-4.824180786646448</v>
       </c>
       <c r="G4">
-        <v>-18.10291331140068</v>
+        <v>-16.25215177507135</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-12.36387800643513</v>
       </c>
       <c r="E5">
-        <v>-21.44874335069562</v>
+        <v>-19.20075451159996</v>
       </c>
       <c r="F5">
-        <v>-5.569873809176952</v>
+        <v>-4.857622807064867</v>
       </c>
       <c r="G5">
-        <v>-17.54587509275077</v>
+        <v>-14.90617500405777</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-12.06847725622954</v>
       </c>
       <c r="E6">
-        <v>-22.80946827746842</v>
+        <v>-20.82111043865453</v>
       </c>
       <c r="F6">
-        <v>-5.660338156501879</v>
+        <v>-4.936793193220026</v>
       </c>
       <c r="G6">
-        <v>-17.61307122906664</v>
+        <v>-14.60229943482681</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-11.74035702116326</v>
       </c>
       <c r="E7">
-        <v>-22.12027076129305</v>
+        <v>-20.62811593339563</v>
       </c>
       <c r="F7">
-        <v>-5.403612187761063</v>
+        <v>-5.28795387424739</v>
       </c>
       <c r="G7">
-        <v>-17.64336346650343</v>
+        <v>-14.44198059004313</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-11.39036236696496</v>
       </c>
       <c r="E8">
-        <v>-23.68337319146864</v>
+        <v>-22.1498190541931</v>
       </c>
       <c r="F8">
-        <v>-5.335114487223572</v>
+        <v>-5.133531279752312</v>
       </c>
       <c r="G8">
-        <v>-17.37437712611405</v>
+        <v>-16.28397962419796</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-11.00417458090198</v>
       </c>
       <c r="E9">
-        <v>-24.28537041215231</v>
+        <v>-21.85623355580182</v>
       </c>
       <c r="F9">
-        <v>-5.178089162348897</v>
+        <v>-5.141998851343728</v>
       </c>
       <c r="G9">
-        <v>-16.58041010171054</v>
+        <v>-14.40141812912527</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-10.59299177068068</v>
       </c>
       <c r="E10">
-        <v>-24.55290359957746</v>
+        <v>-22.34702051180512</v>
       </c>
       <c r="F10">
-        <v>-5.298304324945369</v>
+        <v>-4.770297143829145</v>
       </c>
       <c r="G10">
-        <v>-17.15029594337646</v>
+        <v>-14.26548204174981</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-10.14236859054176</v>
       </c>
       <c r="E11">
-        <v>-25.28449668941264</v>
+        <v>-22.45513330026424</v>
       </c>
       <c r="F11">
-        <v>-5.393090265010703</v>
+        <v>-4.852152268736778</v>
       </c>
       <c r="G11">
-        <v>-16.49132493637161</v>
+        <v>-14.01548413052494</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-9.673359866646415</v>
       </c>
       <c r="E12">
-        <v>-26.24981337973169</v>
+        <v>-23.45899183286258</v>
       </c>
       <c r="F12">
-        <v>-5.143531331038907</v>
+        <v>-4.893675841536909</v>
       </c>
       <c r="G12">
-        <v>-16.5351538533519</v>
+        <v>-14.13626261490654</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-9.189027455521614</v>
       </c>
       <c r="E13">
-        <v>-26.37714501187937</v>
+        <v>-22.80853541182284</v>
       </c>
       <c r="F13">
-        <v>-4.888776876716753</v>
+        <v>-4.172355044731573</v>
       </c>
       <c r="G13">
-        <v>-16.16762258586771</v>
+        <v>-13.10589342080971</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-8.730979594434904</v>
       </c>
       <c r="E14">
-        <v>-27.33509840346196</v>
+        <v>-25.21722167955469</v>
       </c>
       <c r="F14">
-        <v>-4.92029791312808</v>
+        <v>-3.262778643598617</v>
       </c>
       <c r="G14">
-        <v>-15.12946213117798</v>
+        <v>-12.7291173115818</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-8.317545715584616</v>
       </c>
       <c r="E15">
-        <v>-28.09363138516877</v>
+        <v>-25.57610324466256</v>
       </c>
       <c r="F15">
-        <v>-4.349646378115737</v>
+        <v>-3.631868508692174</v>
       </c>
       <c r="G15">
-        <v>-14.65347008504635</v>
+        <v>-13.29688676534187</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-7.992104051330328</v>
       </c>
       <c r="E16">
-        <v>-28.74244849861774</v>
+        <v>-26.7153948494083</v>
       </c>
       <c r="F16">
-        <v>-4.349234679516545</v>
+        <v>-3.627249532054163</v>
       </c>
       <c r="G16">
-        <v>-15.10119440744337</v>
+        <v>-12.81388110812693</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-7.762612746299147</v>
       </c>
       <c r="E17">
-        <v>-30.50940471472262</v>
+        <v>-27.88946966300696</v>
       </c>
       <c r="F17">
-        <v>-4.0266336214355</v>
+        <v>-3.329457249319561</v>
       </c>
       <c r="G17">
-        <v>-13.99076340729609</v>
+        <v>-12.37068651209273</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-7.650412917122859</v>
       </c>
       <c r="E18">
-        <v>-30.81039879659044</v>
+        <v>-27.97143504254579</v>
       </c>
       <c r="F18">
-        <v>-3.828806231768533</v>
+        <v>-3.634201191298457</v>
       </c>
       <c r="G18">
-        <v>-14.12670441650388</v>
+        <v>-11.80510891433437</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-7.639086483858407</v>
       </c>
       <c r="E19">
-        <v>-31.69007298647644</v>
+        <v>-29.33733148663535</v>
       </c>
       <c r="F19">
-        <v>-3.526672475475859</v>
+        <v>-3.382548144532384</v>
       </c>
       <c r="G19">
-        <v>-14.46565132237296</v>
+        <v>-12.40919820953594</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-7.724513474239163</v>
       </c>
       <c r="E20">
-        <v>-31.85165799601813</v>
+        <v>-29.36744583878636</v>
       </c>
       <c r="F20">
-        <v>-3.211924340373353</v>
+        <v>-3.070513741041449</v>
       </c>
       <c r="G20">
-        <v>-14.68332427940496</v>
+        <v>-12.28466272646877</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-7.873451695214037</v>
       </c>
       <c r="E21">
-        <v>-32.32161850006015</v>
+        <v>-29.99761469627175</v>
       </c>
       <c r="F21">
-        <v>-2.841165314963156</v>
+        <v>-2.029023144482284</v>
       </c>
       <c r="G21">
-        <v>-13.93522873240248</v>
+        <v>-12.32714798322046</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-8.069825050279228</v>
       </c>
       <c r="E22">
-        <v>-32.0880284895595</v>
+        <v>-30.82703867433163</v>
       </c>
       <c r="F22">
-        <v>-2.77566961789341</v>
+        <v>-1.926940944333092</v>
       </c>
       <c r="G22">
-        <v>-13.87497730151718</v>
+        <v>-12.35253151320432</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-8.277417954904312</v>
       </c>
       <c r="E23">
-        <v>-33.81896295917037</v>
+        <v>-32.86600447441824</v>
       </c>
       <c r="F23">
-        <v>-2.622316445715346</v>
+        <v>-2.01795532761348</v>
       </c>
       <c r="G23">
-        <v>-13.81016169144269</v>
+        <v>-11.78240614236457</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-8.481119454112395</v>
       </c>
       <c r="E24">
-        <v>-33.61456575636016</v>
+        <v>-32.40916522381345</v>
       </c>
       <c r="F24">
-        <v>-2.678666138290782</v>
+        <v>-1.668110922389165</v>
       </c>
       <c r="G24">
-        <v>-13.93787011575784</v>
+        <v>-12.45126018870646</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-8.650674217854199</v>
       </c>
       <c r="E25">
-        <v>-33.23890619505386</v>
+        <v>-32.78299754585765</v>
       </c>
       <c r="F25">
-        <v>-2.68691502088786</v>
+        <v>-1.852363855426456</v>
       </c>
       <c r="G25">
-        <v>-14.07192770379051</v>
+        <v>-12.57489661706633</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-8.775024571119605</v>
       </c>
       <c r="E26">
-        <v>-35.44284883171392</v>
+        <v>-33.68955955016418</v>
       </c>
       <c r="F26">
-        <v>-2.494675797720178</v>
+        <v>-1.703439135383758</v>
       </c>
       <c r="G26">
-        <v>-14.25199458052972</v>
+        <v>-12.16212878855287</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-8.832677987076313</v>
       </c>
       <c r="E27">
-        <v>-35.20646022427652</v>
+        <v>-33.05952881113603</v>
       </c>
       <c r="F27">
-        <v>-2.508149193526712</v>
+        <v>-1.753746716123175</v>
       </c>
       <c r="G27">
-        <v>-14.75520271888616</v>
+        <v>-12.74366296675481</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-8.819516276598758</v>
       </c>
       <c r="E28">
-        <v>-34.65229048182486</v>
+        <v>-33.55170374442268</v>
       </c>
       <c r="F28">
-        <v>-2.659337013313859</v>
+        <v>-1.980541285498637</v>
       </c>
       <c r="G28">
-        <v>-14.06645626684014</v>
+        <v>-13.59366341172897</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-8.723779842764003</v>
       </c>
       <c r="E29">
-        <v>-34.79216372273678</v>
+        <v>-33.47217015542597</v>
       </c>
       <c r="F29">
-        <v>-2.810701275357801</v>
+        <v>-1.831534557083062</v>
       </c>
       <c r="G29">
-        <v>-14.66212102568783</v>
+        <v>-12.70825858612841</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-8.551394278443651</v>
       </c>
       <c r="E30">
-        <v>-34.38213077947527</v>
+        <v>-31.18637082260327</v>
       </c>
       <c r="F30">
-        <v>-2.636981033847106</v>
+        <v>-1.564772917257329</v>
       </c>
       <c r="G30">
-        <v>-13.61680258616617</v>
+        <v>-12.85277670849259</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-8.303111705848307</v>
       </c>
       <c r="E31">
-        <v>-34.0509476256353</v>
+        <v>-33.63459746113309</v>
       </c>
       <c r="F31">
-        <v>-2.790904951165698</v>
+        <v>-1.935538569606749</v>
       </c>
       <c r="G31">
-        <v>-13.93997009755588</v>
+        <v>-12.6035646498312</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-7.996854617594582</v>
       </c>
       <c r="E32">
-        <v>-33.50014706784535</v>
+        <v>-33.58216678907228</v>
       </c>
       <c r="F32">
-        <v>-2.827734994261567</v>
+        <v>-2.213133598326294</v>
       </c>
       <c r="G32">
-        <v>-14.00797013315381</v>
+        <v>-12.09285563898987</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-7.644294644884344</v>
       </c>
       <c r="E33">
-        <v>-34.15731015889046</v>
+        <v>-33.91023888126897</v>
       </c>
       <c r="F33">
-        <v>-2.833018321556623</v>
+        <v>-2.00830898920788</v>
       </c>
       <c r="G33">
-        <v>-13.53259331606458</v>
+        <v>-11.49254959224634</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-7.268973585361779</v>
       </c>
       <c r="E34">
-        <v>-33.77842858832771</v>
+        <v>-33.60215773757914</v>
       </c>
       <c r="F34">
-        <v>-2.871092572491496</v>
+        <v>-1.983614528563024</v>
       </c>
       <c r="G34">
-        <v>-13.44522422960125</v>
+        <v>-12.46263946507461</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-6.883730189166895</v>
       </c>
       <c r="E35">
-        <v>-34.03207521020834</v>
+        <v>-32.67459040658802</v>
       </c>
       <c r="F35">
-        <v>-2.905661172577723</v>
+        <v>-2.305710282528361</v>
       </c>
       <c r="G35">
-        <v>-13.8429279699353</v>
+        <v>-11.93895650418724</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-6.510931794604386</v>
       </c>
       <c r="E36">
-        <v>-33.47858473885783</v>
+        <v>-31.80745556122926</v>
       </c>
       <c r="F36">
-        <v>-2.767647707964699</v>
+        <v>-2.755986780035491</v>
       </c>
       <c r="G36">
-        <v>-13.95084406580388</v>
+        <v>-12.1318267074514</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-6.160878772918162</v>
       </c>
       <c r="E37">
-        <v>-33.43713335202862</v>
+        <v>-31.75653966372402</v>
       </c>
       <c r="F37">
-        <v>-3.170626911874186</v>
+        <v>-2.282258372987704</v>
       </c>
       <c r="G37">
-        <v>-13.4022336647294</v>
+        <v>-11.78377769297642</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-5.851522392437239</v>
       </c>
       <c r="E38">
-        <v>-31.50039785266517</v>
+        <v>-31.04515715338508</v>
       </c>
       <c r="F38">
-        <v>-3.194068052638606</v>
+        <v>-2.378128645983302</v>
       </c>
       <c r="G38">
-        <v>-13.70043108005174</v>
+        <v>-11.31434316813134</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-5.588596553679062</v>
       </c>
       <c r="E39">
-        <v>-32.52657270517331</v>
+        <v>-31.30677615375621</v>
       </c>
       <c r="F39">
-        <v>-3.027002914842003</v>
+        <v>-2.403544614635996</v>
       </c>
       <c r="G39">
-        <v>-13.04046258169283</v>
+        <v>-11.51324753784332</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-5.38414249560204</v>
       </c>
       <c r="E40">
-        <v>-32.26293853386876</v>
+        <v>-30.86373742768979</v>
       </c>
       <c r="F40">
-        <v>-2.884911397504998</v>
+        <v>-2.230627889506017</v>
       </c>
       <c r="G40">
-        <v>-13.22686549726332</v>
+        <v>-11.33742328058047</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-5.239071984027689</v>
       </c>
       <c r="E41">
-        <v>-31.75928844744668</v>
+        <v>-30.60666954369637</v>
       </c>
       <c r="F41">
-        <v>-3.045573255277962</v>
+        <v>-2.55951625617431</v>
       </c>
       <c r="G41">
-        <v>-12.72953074549829</v>
+        <v>-11.72197588490427</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-5.158875702863266</v>
       </c>
       <c r="E42">
-        <v>-31.12230876505376</v>
+        <v>-30.65895304035192</v>
       </c>
       <c r="F42">
-        <v>-3.387918450404733</v>
+        <v>-2.22911694736331</v>
       </c>
       <c r="G42">
-        <v>-13.44854154459785</v>
+        <v>-10.88637344013296</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-5.138916942629737</v>
       </c>
       <c r="E43">
-        <v>-30.75120937707319</v>
+        <v>-30.32587472013975</v>
       </c>
       <c r="F43">
-        <v>-3.122409302092032</v>
+        <v>-2.832073982717431</v>
       </c>
       <c r="G43">
-        <v>-13.41512886545802</v>
+        <v>-11.54506226208369</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-5.177353895055449</v>
       </c>
       <c r="E44">
-        <v>-30.40869824550304</v>
+        <v>-27.97771603599443</v>
       </c>
       <c r="F44">
-        <v>-3.347191767046095</v>
+        <v>-2.780594262103053</v>
       </c>
       <c r="G44">
-        <v>-13.44616265896725</v>
+        <v>-10.74030329997116</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-5.264183995787332</v>
       </c>
       <c r="E45">
-        <v>-29.3728437798035</v>
+        <v>-30.32706570880377</v>
       </c>
       <c r="F45">
-        <v>-3.600333390034999</v>
+        <v>-2.78959447393447</v>
       </c>
       <c r="G45">
-        <v>-13.06796578080409</v>
+        <v>-10.9094699586899</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-5.388929277864796</v>
       </c>
       <c r="E46">
-        <v>-29.75109815671619</v>
+        <v>-28.68169901980484</v>
       </c>
       <c r="F46">
-        <v>-3.729568645280556</v>
+        <v>-3.476238982891216</v>
       </c>
       <c r="G46">
-        <v>-13.34526837723588</v>
+        <v>-11.07684178921561</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-5.53757642843294</v>
       </c>
       <c r="E47">
-        <v>-29.3969896032124</v>
+        <v>-28.53483607926208</v>
       </c>
       <c r="F47">
-        <v>-3.410199876805234</v>
+        <v>-3.167863478218447</v>
       </c>
       <c r="G47">
-        <v>-12.78553791629645</v>
+        <v>-11.09884566099325</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-5.698617546290751</v>
       </c>
       <c r="E48">
-        <v>-28.20519939929574</v>
+        <v>-27.33793322819076</v>
       </c>
       <c r="F48">
-        <v>-3.284218448717874</v>
+        <v>-2.785721856326382</v>
       </c>
       <c r="G48">
-        <v>-13.20162634102807</v>
+        <v>-11.37126908096615</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-5.862248935190862</v>
       </c>
       <c r="E49">
-        <v>-28.8975215625364</v>
+        <v>-29.05243160139079</v>
       </c>
       <c r="F49">
-        <v>-3.47886159408848</v>
+        <v>-3.075810322214949</v>
       </c>
       <c r="G49">
-        <v>-14.23489121315111</v>
+        <v>-11.08084487951813</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-6.022830169419888</v>
       </c>
       <c r="E50">
-        <v>-27.5787167196526</v>
+        <v>-25.87533122166739</v>
       </c>
       <c r="F50">
-        <v>-3.522379875594551</v>
+        <v>-3.086844176020239</v>
       </c>
       <c r="G50">
-        <v>-13.7420041572099</v>
+        <v>-10.97756186849149</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-6.177917250343973</v>
       </c>
       <c r="E51">
-        <v>-26.40342374654588</v>
+        <v>-27.6452535882473</v>
       </c>
       <c r="F51">
-        <v>-3.419055952708564</v>
+        <v>-3.503923849860179</v>
       </c>
       <c r="G51">
-        <v>-13.53090020573991</v>
+        <v>-10.85531995929438</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-6.327390267926208</v>
       </c>
       <c r="E52">
-        <v>-26.44065233136294</v>
+        <v>-27.30127523109867</v>
       </c>
       <c r="F52">
-        <v>-3.695612208704998</v>
+        <v>-2.706101666671502</v>
       </c>
       <c r="G52">
-        <v>-13.51457612848167</v>
+        <v>-10.4643820978159</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-6.474271937354755</v>
       </c>
       <c r="E53">
-        <v>-26.40226898567393</v>
+        <v>-25.97033860634832</v>
       </c>
       <c r="F53">
-        <v>-3.516393264374519</v>
+        <v>-2.892551430061018</v>
       </c>
       <c r="G53">
-        <v>-13.74009776748387</v>
+        <v>-11.88667023863748</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-6.620673271707944</v>
       </c>
       <c r="E54">
-        <v>-27.05020757516541</v>
+        <v>-25.86751054705615</v>
       </c>
       <c r="F54">
-        <v>-3.435245565228877</v>
+        <v>-3.616230588862124</v>
       </c>
       <c r="G54">
-        <v>-13.64512280944574</v>
+        <v>-10.47847494441371</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-6.771230919198727</v>
       </c>
       <c r="E55">
-        <v>-25.51214307777823</v>
+        <v>-24.54852909368605</v>
       </c>
       <c r="F55">
-        <v>-3.692152946430908</v>
+        <v>-3.450231559912923</v>
       </c>
       <c r="G55">
-        <v>-13.11147477868233</v>
+        <v>-11.78091318655502</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-6.926744786493109</v>
       </c>
       <c r="E56">
-        <v>-25.9181343579879</v>
+        <v>-25.42459408978793</v>
       </c>
       <c r="F56">
-        <v>-3.535983325083325</v>
+        <v>-3.250758204216594</v>
       </c>
       <c r="G56">
-        <v>-13.9972749914808</v>
+        <v>-11.51034693798477</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-7.090835352403503</v>
       </c>
       <c r="E57">
-        <v>-24.90575776578113</v>
+        <v>-23.67890811609708</v>
       </c>
       <c r="F57">
-        <v>-3.693914055529259</v>
+        <v>-3.175383397501061</v>
       </c>
       <c r="G57">
-        <v>-13.9947025137782</v>
+        <v>-11.12694276120677</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-7.261917739761161</v>
       </c>
       <c r="E58">
-        <v>-24.5144930830444</v>
+        <v>-24.2535442968264</v>
       </c>
       <c r="F58">
-        <v>-3.439960632485612</v>
+        <v>-3.047540627859611</v>
       </c>
       <c r="G58">
-        <v>-14.40525387712826</v>
+        <v>-11.8183584869914</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-7.441002011106669</v>
       </c>
       <c r="E59">
-        <v>-24.07563413848706</v>
+        <v>-22.73843916265811</v>
       </c>
       <c r="F59">
-        <v>-3.657074072024557</v>
+        <v>-3.340543290271226</v>
       </c>
       <c r="G59">
-        <v>-13.93194094839992</v>
+        <v>-12.34371815209566</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-7.624611557410208</v>
       </c>
       <c r="E60">
-        <v>-24.06217551373626</v>
+        <v>-22.85564512692463</v>
       </c>
       <c r="F60">
-        <v>-3.541125001552502</v>
+        <v>-3.338045762551786</v>
       </c>
       <c r="G60">
-        <v>-13.39940853296672</v>
+        <v>-12.42994865467786</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-7.812118362942154</v>
       </c>
       <c r="E61">
-        <v>-23.79643107354414</v>
+        <v>-21.84892459875344</v>
       </c>
       <c r="F61">
-        <v>-4.019448362583617</v>
+        <v>-3.512942285774457</v>
       </c>
       <c r="G61">
-        <v>-13.68705025853232</v>
+        <v>-11.82288657274344</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-7.996827221731922</v>
       </c>
       <c r="E62">
-        <v>-23.28436934665281</v>
+        <v>-21.95105527304843</v>
       </c>
       <c r="F62">
-        <v>-3.73447009520292</v>
+        <v>-3.25104399097056</v>
       </c>
       <c r="G62">
-        <v>-14.20042034005836</v>
+        <v>-12.46654411873035</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-8.178632055295711</v>
       </c>
       <c r="E63">
-        <v>-22.21488869720931</v>
+        <v>-22.20778352149128</v>
       </c>
       <c r="F63">
-        <v>-3.90397808847038</v>
+        <v>-2.983133405557143</v>
       </c>
       <c r="G63">
-        <v>-14.29957229314167</v>
+        <v>-12.12740690201082</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-8.350690952284081</v>
       </c>
       <c r="E64">
-        <v>-23.01430021378336</v>
+        <v>-23.31969144391264</v>
       </c>
       <c r="F64">
-        <v>-3.984187247348651</v>
+        <v>-3.329038923781147</v>
       </c>
       <c r="G64">
-        <v>-13.93412460134773</v>
+        <v>-11.79488134673358</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-8.514102803413081</v>
       </c>
       <c r="E65">
-        <v>-22.01664116210152</v>
+        <v>-21.92407009643673</v>
       </c>
       <c r="F65">
-        <v>-4.313916406930786</v>
+        <v>-3.37295979184498</v>
       </c>
       <c r="G65">
-        <v>-14.18225221628372</v>
+        <v>-12.55209212722819</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-8.662646884813817</v>
       </c>
       <c r="E66">
-        <v>-21.87573316487885</v>
+        <v>-21.78498254576514</v>
       </c>
       <c r="F66">
-        <v>-4.18352723589313</v>
+        <v>-3.156432008059814</v>
       </c>
       <c r="G66">
-        <v>-14.21212281675012</v>
+        <v>-12.30315897239936</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-8.799184870711827</v>
       </c>
       <c r="E67">
-        <v>-22.60852630032606</v>
+        <v>-22.8376761420622</v>
       </c>
       <c r="F67">
-        <v>-3.938731414487431</v>
+        <v>-3.07356461818596</v>
       </c>
       <c r="G67">
-        <v>-14.25457198006466</v>
+        <v>-12.86933375248155</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-8.918423840527556</v>
       </c>
       <c r="E68">
-        <v>-22.32355395949737</v>
+        <v>-21.51857241989389</v>
       </c>
       <c r="F68">
-        <v>-4.153053255878941</v>
+        <v>-3.348137762620092</v>
       </c>
       <c r="G68">
-        <v>-14.12790534359464</v>
+        <v>-12.5094132784045</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-9.025105836618048</v>
       </c>
       <c r="E69">
-        <v>-22.04058320418008</v>
+        <v>-21.92018919421215</v>
       </c>
       <c r="F69">
-        <v>-4.133416806595579</v>
+        <v>-3.069696970782289</v>
       </c>
       <c r="G69">
-        <v>-14.39671613863059</v>
+        <v>-11.86143108240223</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-9.11463254719048</v>
       </c>
       <c r="E70">
-        <v>-21.54473794271021</v>
+        <v>-21.47499944299209</v>
       </c>
       <c r="F70">
-        <v>-3.971707064058073</v>
+        <v>-3.375960138577919</v>
       </c>
       <c r="G70">
-        <v>-14.09198252996184</v>
+        <v>-12.1998529928218</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-9.193391479999672</v>
       </c>
       <c r="E71">
-        <v>-21.8813122448563</v>
+        <v>-21.64507081282416</v>
       </c>
       <c r="F71">
-        <v>-4.468160074066859</v>
+        <v>-3.128146574723822</v>
       </c>
       <c r="G71">
-        <v>-13.54182995475442</v>
+        <v>-12.47477998484456</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-9.257302774953077</v>
       </c>
       <c r="E72">
-        <v>-20.85213048560707</v>
+        <v>-22.37482081373821</v>
       </c>
       <c r="F72">
-        <v>-4.267147611736128</v>
+        <v>-3.331944008262765</v>
       </c>
       <c r="G72">
-        <v>-14.08154168295968</v>
+        <v>-12.94957930693933</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-9.313468631576884</v>
       </c>
       <c r="E73">
-        <v>-22.21769635109407</v>
+        <v>-22.01581245135812</v>
       </c>
       <c r="F73">
-        <v>-4.206526856831857</v>
+        <v>-3.52819087292519</v>
       </c>
       <c r="G73">
-        <v>-13.6775215911237</v>
+        <v>-11.43305120170893</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-9.356437076604841</v>
       </c>
       <c r="E74">
-        <v>-21.70045404993796</v>
+        <v>-21.99539356205753</v>
       </c>
       <c r="F74">
-        <v>-4.565723530033779</v>
+        <v>-3.520857336308206</v>
       </c>
       <c r="G74">
-        <v>-13.65115697589356</v>
+        <v>-12.65824948834091</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-9.392509888099667</v>
       </c>
       <c r="E75">
-        <v>-20.46341080526265</v>
+        <v>-21.89971596322347</v>
       </c>
       <c r="F75">
-        <v>-4.532829888836013</v>
+        <v>-3.524753148203572</v>
       </c>
       <c r="G75">
-        <v>-13.86497941942555</v>
+        <v>-11.44120175606259</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-9.414637988193578</v>
       </c>
       <c r="E76">
-        <v>-21.70899475191643</v>
+        <v>-22.92303334863277</v>
       </c>
       <c r="F76">
-        <v>-4.518975444024192</v>
+        <v>-3.392911849108808</v>
       </c>
       <c r="G76">
-        <v>-13.60729032486534</v>
+        <v>-11.27875832031916</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-9.427155687726593</v>
       </c>
       <c r="E77">
-        <v>-22.43157165000233</v>
+        <v>-21.51731350411976</v>
       </c>
       <c r="F77">
-        <v>-4.337413048311194</v>
+        <v>-3.679337274342196</v>
       </c>
       <c r="G77">
-        <v>-13.02350194745206</v>
+        <v>-11.27916847301409</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-9.42298200141957</v>
       </c>
       <c r="E78">
-        <v>-23.05817206996968</v>
+        <v>-23.0012129239012</v>
       </c>
       <c r="F78">
-        <v>-4.548695609701833</v>
+        <v>-4.217902826374504</v>
       </c>
       <c r="G78">
-        <v>-13.27984738178368</v>
+        <v>-10.43059864063986</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-9.407426668308833</v>
       </c>
       <c r="E79">
-        <v>-22.8637737377684</v>
+        <v>-23.02718825080919</v>
       </c>
       <c r="F79">
-        <v>-4.567154120538414</v>
+        <v>-3.844411016902471</v>
       </c>
       <c r="G79">
-        <v>-13.23616119794123</v>
+        <v>-10.1502674767087</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-9.372219579100628</v>
       </c>
       <c r="E80">
-        <v>-23.66282297642184</v>
+        <v>-24.29358959247623</v>
       </c>
       <c r="F80">
-        <v>-4.808509732120286</v>
+        <v>-3.980559826491792</v>
       </c>
       <c r="G80">
-        <v>-12.91761036528566</v>
+        <v>-10.90567358534562</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-9.323769667659972</v>
       </c>
       <c r="E81">
-        <v>-23.74933041539036</v>
+        <v>-24.86082171820301</v>
       </c>
       <c r="F81">
-        <v>-4.803197411966133</v>
+        <v>-3.592711581561841</v>
       </c>
       <c r="G81">
-        <v>-12.60773836365482</v>
+        <v>-10.72578389457062</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-9.254839836688541</v>
       </c>
       <c r="E82">
-        <v>-24.63212925234165</v>
+        <v>-24.62194018582439</v>
       </c>
       <c r="F82">
-        <v>-4.932706028454613</v>
+        <v>-4.623961900287599</v>
       </c>
       <c r="G82">
-        <v>-12.26030621883301</v>
+        <v>-9.751077343008212</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-9.1747427886409</v>
       </c>
       <c r="E83">
-        <v>-24.96616308056944</v>
+        <v>-25.86533235105846</v>
       </c>
       <c r="F83">
-        <v>-5.032326320682685</v>
+        <v>-4.249853785467883</v>
       </c>
       <c r="G83">
-        <v>-13.11143868524517</v>
+        <v>-11.90960925855956</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-9.077532775023817</v>
       </c>
       <c r="E84">
-        <v>-25.27684809681368</v>
+        <v>-25.90280547347193</v>
       </c>
       <c r="F84">
-        <v>-4.940949940847274</v>
+        <v>-4.346795965882704</v>
       </c>
       <c r="G84">
-        <v>-11.75924071815489</v>
+        <v>-10.88178957361442</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-8.974897253048347</v>
       </c>
       <c r="E85">
-        <v>-26.4050856965067</v>
+        <v>-27.24637654070368</v>
       </c>
       <c r="F85">
-        <v>-5.168828843153001</v>
+        <v>-4.241160897942905</v>
       </c>
       <c r="G85">
-        <v>-12.21946157286104</v>
+        <v>-11.37393999531553</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-8.861880933263219</v>
       </c>
       <c r="E86">
-        <v>-27.40984539543257</v>
+        <v>-27.86785072809434</v>
       </c>
       <c r="F86">
-        <v>-5.295669288237065</v>
+        <v>-4.607467448563055</v>
       </c>
       <c r="G86">
-        <v>-12.24429057640136</v>
+        <v>-10.21637096624527</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-8.754866210523806</v>
       </c>
       <c r="E87">
-        <v>-28.4467617882869</v>
+        <v>-29.48303060935814</v>
       </c>
       <c r="F87">
-        <v>-5.288050793233517</v>
+        <v>-4.829182469024551</v>
       </c>
       <c r="G87">
-        <v>-12.7919658293314</v>
+        <v>-10.42495165833605</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-8.652998044333247</v>
       </c>
       <c r="E88">
-        <v>-29.61216004568686</v>
+        <v>-29.52795080727723</v>
       </c>
       <c r="F88">
-        <v>-5.187845673619069</v>
+        <v>-4.602416892508186</v>
       </c>
       <c r="G88">
-        <v>-11.89341314894214</v>
+        <v>-10.19667379322392</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-8.578417163742072</v>
       </c>
       <c r="E89">
-        <v>-31.06044528163497</v>
+        <v>-30.77252037575328</v>
       </c>
       <c r="F89">
-        <v>-5.42477117633077</v>
+        <v>-4.688490064230875</v>
       </c>
       <c r="G89">
-        <v>-12.18144862109488</v>
+        <v>-11.20557067343575</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-8.531426941833891</v>
       </c>
       <c r="E90">
-        <v>-32.09339246702159</v>
+        <v>-34.02006116866599</v>
       </c>
       <c r="F90">
-        <v>-5.336584010996138</v>
+        <v>-4.839555285642406</v>
       </c>
       <c r="G90">
-        <v>-12.6616324277687</v>
+        <v>-10.15513024705979</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-8.535918532724335</v>
       </c>
       <c r="E91">
-        <v>-34.43697739241917</v>
+        <v>-34.55995716104547</v>
       </c>
       <c r="F91">
-        <v>-5.706365562871031</v>
+        <v>-5.199840433611606</v>
       </c>
       <c r="G91">
-        <v>-12.50636502357577</v>
+        <v>-10.61003552283965</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-8.588815858364036</v>
       </c>
       <c r="E92">
-        <v>-35.35127629456781</v>
+        <v>-36.40072523923838</v>
       </c>
       <c r="F92">
-        <v>-5.440621158215936</v>
+        <v>-4.960578106456609</v>
       </c>
       <c r="G92">
-        <v>-12.76851822006761</v>
+        <v>-10.94427387577093</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-8.711909597677439</v>
       </c>
       <c r="E93">
-        <v>-37.35746952826091</v>
+        <v>-37.18178737913334</v>
       </c>
       <c r="F93">
-        <v>-5.485330632047233</v>
+        <v>-5.170102043851104</v>
       </c>
       <c r="G93">
-        <v>-12.81895387665783</v>
+        <v>-11.40426176374636</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-8.896524843249955</v>
       </c>
       <c r="E94">
-        <v>-38.62284969903922</v>
+        <v>-38.57274666261836</v>
       </c>
       <c r="F94">
-        <v>-5.41269275123055</v>
+        <v>-4.710696937565124</v>
       </c>
       <c r="G94">
-        <v>-13.20897627732123</v>
+        <v>-12.42039373749676</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-9.157634871306408</v>
       </c>
       <c r="E95">
-        <v>-40.78916071669553</v>
+        <v>-41.7874831898195</v>
       </c>
       <c r="F95">
-        <v>-5.470617170238709</v>
+        <v>-5.127674722214519</v>
       </c>
       <c r="G95">
-        <v>-14.03700566273334</v>
+        <v>-11.51945889025535</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-9.483821730051645</v>
       </c>
       <c r="E96">
-        <v>-42.28732030112712</v>
+        <v>-44.35504643963645</v>
       </c>
       <c r="F96">
-        <v>-5.225287880225607</v>
+        <v>-5.373635228188554</v>
       </c>
       <c r="G96">
-        <v>-14.06895491705765</v>
+        <v>-12.26083449550408</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-9.87732237091358</v>
       </c>
       <c r="E97">
-        <v>-44.71001766743871</v>
+        <v>-46.21651417251842</v>
       </c>
       <c r="F97">
-        <v>-5.318858605311034</v>
+        <v>-4.908023164953397</v>
       </c>
       <c r="G97">
-        <v>-13.98106739758793</v>
+        <v>-12.78178091761088</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-10.32996922810275</v>
       </c>
       <c r="E98">
-        <v>-46.4880822302844</v>
+        <v>-47.87388584611168</v>
       </c>
       <c r="F98">
-        <v>-5.517173903378249</v>
+        <v>-4.800572315666662</v>
       </c>
       <c r="G98">
-        <v>-14.55668061148585</v>
+        <v>-13.24668407548237</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-10.82589761618366</v>
       </c>
       <c r="E99">
-        <v>-48.70353058727944</v>
+        <v>-51.17969451408108</v>
       </c>
       <c r="F99">
-        <v>-5.204605202912509</v>
+        <v>-5.03541116089071</v>
       </c>
       <c r="G99">
-        <v>-14.65458077854423</v>
+        <v>-12.86343739733922</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-11.37356409614882</v>
       </c>
       <c r="E100">
-        <v>-50.59332845355339</v>
+        <v>-52.36055977445424</v>
       </c>
       <c r="F100">
-        <v>-4.965322994939844</v>
+        <v>-4.881291748865056</v>
       </c>
       <c r="G100">
-        <v>-15.01419281779469</v>
+        <v>-12.67148593611171</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-11.92251472932429</v>
       </c>
       <c r="E101">
-        <v>-53.23425751076861</v>
+        <v>-54.9068697636347</v>
       </c>
       <c r="F101">
-        <v>-4.998395563496614</v>
+        <v>-4.522539908958438</v>
       </c>
       <c r="G101">
-        <v>-15.71321769637567</v>
+        <v>-14.07254293283291</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-12.53553102035965</v>
       </c>
       <c r="E102">
-        <v>-55.27653022899933</v>
+        <v>-56.53854800782694</v>
       </c>
       <c r="F102">
-        <v>-5.08695052395809</v>
+        <v>-5.065630003744836</v>
       </c>
       <c r="G102">
-        <v>-15.87434208105221</v>
+        <v>-15.20919909629405</v>
       </c>
     </row>
   </sheetData>
